--- a/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
+++ b/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BFBE38-4DB9-400E-A40C-60C2B3CF33DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE9204D-4D97-45C3-83C6-6BC087ACCAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -344,10 +333,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Portrait/StoryNpc/gu_wen/gu_wen.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <r>
       <t>老</t>
     </r>
@@ -371,6 +356,10 @@
       </rPr>
       <t>心阳虚</t>
     </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/gu_wen/gu_wen_sick.png</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -378,11 +367,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -396,7 +385,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -417,7 +406,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -561,7 +550,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -840,27 +829,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -910,12 +899,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="36" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="54">
       <c r="A2" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>21</v>
@@ -941,7 +930,7 @@
         <v>43</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -952,62 +941,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="17"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16">
       <c r="C4" s="10"/>
       <c r="H4" s="17"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16">
       <c r="C5" s="10"/>
       <c r="H5" s="17"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16">
       <c r="H6" s="17"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16">
       <c r="H7" s="17"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16">
       <c r="H8" s="17"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16">
       <c r="H9" s="17"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16">
       <c r="H10" s="17"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16">
       <c r="H11" s="17"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16">
       <c r="H12" s="17"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16">
       <c r="H13" s="17"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16">
       <c r="H14" s="17"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16">
       <c r="H15" s="17"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16">
       <c r="H16" s="17"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8">
       <c r="H17" s="17"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8">
       <c r="H18" s="17"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8">
       <c r="H19" s="17"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="17"/>
     </row>
   </sheetData>
@@ -1019,20 +1008,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1058,7 +1047,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1082,7 +1071,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1104,7 +1093,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1126,7 +1115,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1148,7 +1137,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1170,7 +1159,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="3">
         <v>6</v>
       </c>

--- a/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
+++ b/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE9204D-4D97-45C3-83C6-6BC087ACCAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CD3A24-30B9-4892-9480-1C8847C3A67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -918,9 +918,7 @@
       <c r="F2" s="1">
         <v>3</v>
       </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">

--- a/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
+++ b/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CD3A24-30B9-4892-9480-1C8847C3A67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D373BF-96BA-4A52-98A5-587AF4F0679E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -359,7 +370,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Portrait/StoryNpc/gu_wen/gu_wen_sick.png</t>
+    <t>res://Assets/Portrait/StoryNpc/gu_wen/gu_wen.png</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -367,11 +378,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -385,7 +396,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -406,7 +417,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -550,7 +561,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -829,27 +840,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -899,7 +910,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="54">
+    <row r="2" spans="1:16" ht="36" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>39</v>
       </c>
@@ -939,62 +950,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="10"/>
       <c r="H3" s="17"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="10"/>
       <c r="H4" s="17"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="10"/>
       <c r="H5" s="17"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H6" s="17"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H7" s="17"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="17"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="17"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="17"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="17"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="17"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="17"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="17"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="17"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="17"/>
     </row>
-    <row r="17" spans="8:8">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="17"/>
     </row>
-    <row r="18" spans="8:8">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="17"/>
     </row>
-    <row r="19" spans="8:8">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="17"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="17"/>
     </row>
   </sheetData>
@@ -1006,20 +1017,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1045,7 +1056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1069,7 +1080,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1091,7 +1102,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1113,7 +1124,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1135,7 +1146,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1157,7 +1168,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>

--- a/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
+++ b/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D373BF-96BA-4A52-98A5-587AF4F0679E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D6D429-45BE-4C6A-A383-8F1A3BDB5D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>StoryID</t>
   </si>
@@ -154,9 +143,61 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>和我学了一年多医</t>
-    </r>
+    <t>李东璧</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>顾先生，学生有礼了。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ClinicNpcPortraitPath</t>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>004/004.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerReputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerEntryId</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>gu_wen</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>004_01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -165,7 +206,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>术</t>
+      <t>东璧近来如何啊</t>
     </r>
     <r>
       <rPr>
@@ -175,7 +216,25 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>，</t>
+      <t>？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>正好我这几日不怎么舒服，东璧你给我看看。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Disease</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>心阳虚</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>老</t>
     </r>
     <r>
       <rPr>
@@ -185,7 +244,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>现</t>
+      <t>师</t>
     </r>
     <r>
       <rPr>
@@ -195,7 +254,17 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>在啊已</t>
+      <t>心阳虚</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/gu_wen/gu_wen.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>和我学了一年多医</t>
     </r>
     <r>
       <rPr>
@@ -205,7 +274,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>经</t>
+      <t>术</t>
     </r>
     <r>
       <rPr>
@@ -215,7 +284,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>能自己出</t>
+      <t>，</t>
     </r>
     <r>
       <rPr>
@@ -225,7 +294,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>诊</t>
+      <t>现</t>
     </r>
     <r>
       <rPr>
@@ -235,6 +304,46 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
+      <t>在啊已</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>经</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>能自己出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>诊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
       <t>了。</t>
     </r>
     <r>
@@ -245,132 +354,8 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>你还别说，这小子还真是块学医的材料。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>李东璧</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>顾先生，学生有礼了。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>dim</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <r>
-      <t>res://Assets/Background/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>004/004.png</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>gu_wen</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>004_01</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>东璧近来如何啊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>？</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>正好我这几日不怎么舒服，东璧你给我看看。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>心阳虚</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>老</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>师</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>心阳虚</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/gu_wen/gu_wen.png</t>
+      <t>你还别说，这小子学得还挺快。</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -378,11 +363,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -396,7 +381,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -417,7 +402,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -561,7 +546,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -840,27 +825,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -880,28 +865,28 @@
         <v>16</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>17</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O1" s="18" t="s">
         <v>18</v>
@@ -910,12 +895,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="36" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="54">
       <c r="A2" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>21</v>
@@ -933,13 +918,13 @@
       <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -950,62 +935,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="17"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16">
       <c r="C4" s="10"/>
       <c r="H4" s="17"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16">
       <c r="C5" s="10"/>
       <c r="H5" s="17"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16">
       <c r="H6" s="17"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16">
       <c r="H7" s="17"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16">
       <c r="H8" s="17"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16">
       <c r="H9" s="17"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16">
       <c r="H10" s="17"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16">
       <c r="H11" s="17"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16">
       <c r="H12" s="17"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16">
       <c r="H13" s="17"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16">
       <c r="H14" s="17"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16">
       <c r="H15" s="17"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16">
       <c r="H16" s="17"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8">
       <c r="H17" s="17"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8">
       <c r="H18" s="17"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8">
       <c r="H19" s="17"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="17"/>
     </row>
   </sheetData>
@@ -1017,20 +1002,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1056,7 +1041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1067,20 +1052,18 @@
         <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="8"/>
+      <c r="G2" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1094,15 +1077,13 @@
         <v>11</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1113,18 +1094,16 @@
         <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1138,15 +1117,13 @@
         <v>11</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="F5" s="8"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1154,21 +1131,19 @@
         <v>6</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="F6" s="8"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1179,15 +1154,13 @@
         <v>23</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="F7" s="8"/>
       <c r="G7" s="3"/>
       <c r="H7" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
+++ b/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D6D429-45BE-4C6A-A383-8F1A3BDB5D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F36049-7085-453F-A7BB-54185EDB9752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -354,7 +365,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>你还别说，这小子学得还挺快。</t>
+      <t>你还别说，这小子学得挺快，医馆让他打理我也清闲许多。</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
@@ -363,11 +374,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -381,7 +392,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -402,7 +413,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -546,7 +557,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -825,27 +836,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -895,7 +906,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="54">
+    <row r="2" spans="1:16" ht="36" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>37</v>
       </c>
@@ -935,62 +946,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="10"/>
       <c r="H3" s="17"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="10"/>
       <c r="H4" s="17"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="10"/>
       <c r="H5" s="17"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H6" s="17"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H7" s="17"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="17"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="17"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="17"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="17"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="17"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="17"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="17"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="17"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="17"/>
     </row>
-    <row r="17" spans="8:8">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="17"/>
     </row>
-    <row r="18" spans="8:8">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="17"/>
     </row>
-    <row r="19" spans="8:8">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="17"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="17"/>
     </row>
   </sheetData>
@@ -1002,20 +1013,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1041,7 +1052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1063,7 +1074,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1083,7 +1094,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1103,7 +1114,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1123,7 +1134,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1143,7 +1154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>

--- a/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
+++ b/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F36049-7085-453F-A7BB-54185EDB9752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB83818-7579-4F25-A1DD-96F1A3A9E552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
   <si>
     <t>LineIndex</t>
   </si>
@@ -84,33 +70,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
-  </si>
-  <si>
-    <t>scene_enter</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>night</t>
@@ -162,9 +125,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
     <r>
       <t>res://Assets/Background/</t>
     </r>
@@ -181,26 +141,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>gu_wen</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -236,10 +176,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>心阳虚</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -368,17 +304,102 @@
       <t>你还别说，这小子学得挺快，医馆让他打理我也清闲许多。</t>
     </r>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="9"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -392,7 +413,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -413,7 +434,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -435,13 +456,27 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -456,20 +491,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -500,7 +537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -526,9 +563,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -544,20 +578,43 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -835,177 +892,204 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.265625" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:20" s="22" customFormat="1">
+      <c r="A1" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="P1" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q1" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R1" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S1" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" s="22" customFormat="1" ht="36">
+      <c r="A2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="O1" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="P1" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="36" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="11">
+        <v>3</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="1">
-        <v>3</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1" t="b">
+      <c r="N2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C3" s="10"/>
-      <c r="H3" s="17"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C4" s="10"/>
-      <c r="H4" s="17"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C5" s="10"/>
-      <c r="H5" s="17"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H6" s="17"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H7" s="17"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H8" s="17"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H9" s="17"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H10" s="17"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H11" s="17"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H12" s="17"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H13" s="17"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H14" s="17"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H15" s="17"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H16" s="17"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H17" s="17"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H18" s="17"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H19" s="17"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H20" s="17"/>
+      <c r="T2" s="24"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="9"/>
+      <c r="H3" s="14"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="9"/>
+      <c r="H4" s="14"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="9"/>
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="H7" s="14"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="H8" s="14"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="14"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="14"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="14"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" spans="8:8">
+      <c r="H18" s="14"/>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" s="14"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{A2EC3B2D-55F8-4960-BD06-DF54867B0CAA}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{4E3C7C41-C6FC-43BD-96BC-A54415F71777}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{D29ED2AA-5CE5-46BA-8EA1-B46337ADF3DD}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{84F9C380-F06B-4C4F-AEF4-170A5BF609AB}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{F3152902-9414-4BAC-865A-2D2DC344B62A}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1013,165 +1097,165 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H4" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="33">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>27</v>
+        <v>5</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="8"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="8"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="14" t="s">
-        <v>39</v>
+      <c r="H7" s="13" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
+++ b/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB83818-7579-4F25-A1DD-96F1A3A9E552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76CAFA3-D5E0-4F2C-A8EA-898A4330ED84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>

--- a/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
+++ b/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76CAFA3-D5E0-4F2C-A8EA-898A4330ED84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EDB99B-3156-4A79-BF61-C338695F577E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19740" yWindow="5400" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
   <si>
     <t>LineIndex</t>
   </si>
@@ -388,6 +399,10 @@
   </si>
   <si>
     <t>奖励心得</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>Music</t>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -399,7 +414,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -413,7 +428,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -434,7 +449,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -537,7 +552,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -612,9 +627,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -893,25 +911,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.86328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28.265625" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.25" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="22" customFormat="1">
+    <row r="1" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A1" s="15" t="s">
         <v>30</v>
       </c>
@@ -1096,21 +1114,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1135,8 +1153,11 @@
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1157,8 +1178,9 @@
       <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1177,8 +1199,9 @@
       <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1197,8 +1220,9 @@
       <c r="H4" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="33">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1217,8 +1241,9 @@
       <c r="H5" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1237,8 +1262,9 @@
       <c r="H6" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1257,6 +1283,7 @@
       <c r="H7" s="13" t="s">
         <v>25</v>
       </c>
+      <c r="I7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
+++ b/DataTables/DetailText/剧情/004_01老师心阳虚.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EDB99B-3156-4A79-BF61-C338695F577E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6740B2FE-A954-4FF2-B4F3-B8B96ECB5DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19740" yWindow="5400" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -221,102 +221,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>和我学了一年多医</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>术</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>现</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>在啊已</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>经</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>能自己出</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>诊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>了。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你还别说，这小子学得挺快，医馆让他打理我也清闲许多。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>剧情ID</t>
     <phoneticPr fontId="9"/>
   </si>
@@ -404,6 +308,102 @@
   <si>
     <t>Music</t>
     <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>和我学了一年多医</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>在啊已</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>经</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>能自己出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>诊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>了。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你还别说，这小子学得挺快，医馆让他打理，我也清闲许多。</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -931,58 +931,58 @@
   <sheetData>
     <row r="1" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A1" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="H1" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="I1" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="J1" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="K1" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="L1" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="M1" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="O1" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="P1" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="R1" s="20" t="s">
         <v>46</v>
-      </c>
-      <c r="R1" s="20" t="s">
-        <v>47</v>
       </c>
       <c r="S1" s="21" t="s">
         <v>12</v>
@@ -1154,7 +1154,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" ht="34.5">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1239,7 +1239,7 @@
       <c r="F5" s="8"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I5" s="1"/>
     </row>
